--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/NEW_HAMPSHIRE_2019.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/NEW_HAMPSHIRE_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -457,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California Sur</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -488,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Las Margaritas</t>
@@ -501,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Pijijiapan</t>
@@ -514,9 +539,14 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Cristóbal de las Casas</t>
+          <t>San Cristóbal De Las Casas</t>
         </is>
       </c>
       <c r="C11">
@@ -527,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Tapachula</t>
@@ -540,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Tenejapa</t>
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Total</t>
@@ -584,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -615,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Total</t>
@@ -630,7 +685,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -646,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -659,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -672,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Total</t>
@@ -703,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -716,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -731,7 +811,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -747,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Coatepec Harinas</t>
@@ -760,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -773,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Temoaya</t>
@@ -786,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -799,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Total</t>
@@ -819,7 +924,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C32">
@@ -830,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -843,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -856,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Total</t>
@@ -887,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Malinaltepec</t>
@@ -900,9 +1025,14 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mártir de Cuilapan</t>
+          <t>Mártir De Cuilapan</t>
         </is>
       </c>
       <c r="C38">
@@ -913,9 +1043,14 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Taxco de Alarcón</t>
+          <t>Taxco De Alarcón</t>
         </is>
       </c>
       <c r="C39">
@@ -926,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Teloloapan</t>
@@ -939,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Total</t>
@@ -970,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -983,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -996,6 +1151,11 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>Zapopan</t>
@@ -1009,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Zapotiltic</t>
@@ -1022,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1053,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -1066,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1086,7 +1266,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C51">
@@ -1097,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1128,9 +1313,14 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Huehuetlán el Chico</t>
+          <t>Huehuetlán El Chico</t>
         </is>
       </c>
       <c r="C54">
@@ -1141,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -1154,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -1167,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1198,9 +1403,14 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C59">
@@ -1211,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C60">
@@ -1224,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -1237,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1268,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1299,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1330,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1350,7 +1590,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Alto Lucero de Gutiérrez Barrios</t>
+          <t>Alto Lucero De Gutiérrez Barrios</t>
         </is>
       </c>
       <c r="C69">
@@ -1361,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Altotonga</t>
@@ -1374,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -1387,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Soledad de Doblado</t>
+          <t>Soledad De Doblado</t>
         </is>
       </c>
       <c r="C72">
@@ -1400,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1431,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1454,41 +1719,6 @@
       </c>
       <c r="D76">
         <v>1</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
